--- a/docs/poem-asaka-shift-schedule.xlsx
+++ b/docs/poem-asaka-shift-schedule.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務形態一覧表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第1週" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第2週" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第3週" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="第4週" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -111,6 +115,50 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E3DCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E3DCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3DCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E3DCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3DCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E3DCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E3DCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E3DCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00888888"/>
       </left>
@@ -168,55 +216,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E3DCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E3DCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E3DCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E3DCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E3DCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E3DCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E3DCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E3DCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -227,13 +231,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,26 +249,25 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -627,7 +633,1053 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務形態一覧表（4週分・集計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>poem de riha 安積店</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護（3時間以上4時間未満）／ 介護予防・日常生活支援総合事業</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>福島県郡山市安積町笹川字四角担3-1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>基準年月</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>令和8年（2026年）6月</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>サービス提供時間</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>午前 9:00〜12:05 ／ 午後 13:25〜16:30</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>営業日</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>月〜金（祝日も営業）／ 休：土日・年末年始</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>雇用形態</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>第1週
+合計(h)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>第2週
+合計(h)</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>第3週
+合計(h)</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>第4週
+合計(h)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>4週合計
+(h)</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>月平均
+(h/週)</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>常勤換算
+(月/160h)</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="M7" s="7" t="n"/>
+      <c r="N7" s="7" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="9">
+        <f>'第1週'!L8</f>
+        <v/>
+      </c>
+      <c r="F8" s="9">
+        <f>'第2週'!L8</f>
+        <v/>
+      </c>
+      <c r="G8" s="9">
+        <f>'第3週'!L8</f>
+        <v/>
+      </c>
+      <c r="H8" s="9">
+        <f>'第4週'!L8</f>
+        <v/>
+      </c>
+      <c r="I8" s="10">
+        <f>SUM(E8:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="10">
+        <f>I8/4</f>
+        <v/>
+      </c>
+      <c r="K8" s="11">
+        <f>I8/160</f>
+        <v/>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>生活相談員</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
+      <c r="E9" s="9">
+        <f>'第1週'!L9</f>
+        <v/>
+      </c>
+      <c r="F9" s="9">
+        <f>'第2週'!L9</f>
+        <v/>
+      </c>
+      <c r="G9" s="9">
+        <f>'第3週'!L9</f>
+        <v/>
+      </c>
+      <c r="H9" s="9">
+        <f>'第4週'!L9</f>
+        <v/>
+      </c>
+      <c r="I9" s="10">
+        <f>SUM(E9:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="10">
+        <f>I9/4</f>
+        <v/>
+      </c>
+      <c r="K9" s="11">
+        <f>I9/160</f>
+        <v/>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>看護職員</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
+      <c r="E10" s="9">
+        <f>'第1週'!L10</f>
+        <v/>
+      </c>
+      <c r="F10" s="9">
+        <f>'第2週'!L10</f>
+        <v/>
+      </c>
+      <c r="G10" s="9">
+        <f>'第3週'!L10</f>
+        <v/>
+      </c>
+      <c r="H10" s="9">
+        <f>'第4週'!L10</f>
+        <v/>
+      </c>
+      <c r="I10" s="10">
+        <f>SUM(E10:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="10">
+        <f>I10/4</f>
+        <v/>
+      </c>
+      <c r="K10" s="11">
+        <f>I10/160</f>
+        <v/>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>機能訓練指導員</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="9">
+        <f>'第1週'!L11</f>
+        <v/>
+      </c>
+      <c r="F11" s="9">
+        <f>'第2週'!L11</f>
+        <v/>
+      </c>
+      <c r="G11" s="9">
+        <f>'第3週'!L11</f>
+        <v/>
+      </c>
+      <c r="H11" s="9">
+        <f>'第4週'!L11</f>
+        <v/>
+      </c>
+      <c r="I11" s="10">
+        <f>SUM(E11:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="10">
+        <f>I11/4</f>
+        <v/>
+      </c>
+      <c r="K11" s="11">
+        <f>I11/160</f>
+        <v/>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>柔道整復師</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+      <c r="E12" s="9">
+        <f>'第1週'!L12</f>
+        <v/>
+      </c>
+      <c r="F12" s="9">
+        <f>'第2週'!L12</f>
+        <v/>
+      </c>
+      <c r="G12" s="9">
+        <f>'第3週'!L12</f>
+        <v/>
+      </c>
+      <c r="H12" s="9">
+        <f>'第4週'!L12</f>
+        <v/>
+      </c>
+      <c r="I12" s="10">
+        <f>SUM(E12:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="10">
+        <f>I12/4</f>
+        <v/>
+      </c>
+      <c r="K12" s="11">
+        <f>I12/160</f>
+        <v/>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="9">
+        <f>'第1週'!L13</f>
+        <v/>
+      </c>
+      <c r="F13" s="9">
+        <f>'第2週'!L13</f>
+        <v/>
+      </c>
+      <c r="G13" s="9">
+        <f>'第3週'!L13</f>
+        <v/>
+      </c>
+      <c r="H13" s="9">
+        <f>'第4週'!L13</f>
+        <v/>
+      </c>
+      <c r="I13" s="10">
+        <f>SUM(E13:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="10">
+        <f>I13/4</f>
+        <v/>
+      </c>
+      <c r="K13" s="11">
+        <f>I13/160</f>
+        <v/>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>非常勤専従</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
+      <c r="E14" s="9">
+        <f>'第1週'!L14</f>
+        <v/>
+      </c>
+      <c r="F14" s="9">
+        <f>'第2週'!L14</f>
+        <v/>
+      </c>
+      <c r="G14" s="9">
+        <f>'第3週'!L14</f>
+        <v/>
+      </c>
+      <c r="H14" s="9">
+        <f>'第4週'!L14</f>
+        <v/>
+      </c>
+      <c r="I14" s="10">
+        <f>SUM(E14:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="10">
+        <f>I14/4</f>
+        <v/>
+      </c>
+      <c r="K14" s="11">
+        <f>I14/160</f>
+        <v/>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>非常勤専従</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="9">
+        <f>'第1週'!L15</f>
+        <v/>
+      </c>
+      <c r="F15" s="9">
+        <f>'第2週'!L15</f>
+        <v/>
+      </c>
+      <c r="G15" s="9">
+        <f>'第3週'!L15</f>
+        <v/>
+      </c>
+      <c r="H15" s="9">
+        <f>'第4週'!L15</f>
+        <v/>
+      </c>
+      <c r="I15" s="10">
+        <f>SUM(E15:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="10">
+        <f>I15/4</f>
+        <v/>
+      </c>
+      <c r="K15" s="11">
+        <f>I15/160</f>
+        <v/>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+      <c r="E16" s="9">
+        <f>'第1週'!L16</f>
+        <v/>
+      </c>
+      <c r="F16" s="9">
+        <f>'第2週'!L16</f>
+        <v/>
+      </c>
+      <c r="G16" s="9">
+        <f>'第3週'!L16</f>
+        <v/>
+      </c>
+      <c r="H16" s="9">
+        <f>'第4週'!L16</f>
+        <v/>
+      </c>
+      <c r="I16" s="10">
+        <f>SUM(E16:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="10">
+        <f>I16/4</f>
+        <v/>
+      </c>
+      <c r="K16" s="11">
+        <f>I16/160</f>
+        <v/>
+      </c>
+      <c r="L16" s="3" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+      <c r="E17" s="9">
+        <f>'第1週'!L17</f>
+        <v/>
+      </c>
+      <c r="F17" s="9">
+        <f>'第2週'!L17</f>
+        <v/>
+      </c>
+      <c r="G17" s="9">
+        <f>'第3週'!L17</f>
+        <v/>
+      </c>
+      <c r="H17" s="9">
+        <f>'第4週'!L17</f>
+        <v/>
+      </c>
+      <c r="I17" s="10">
+        <f>SUM(E17:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="10">
+        <f>I17/4</f>
+        <v/>
+      </c>
+      <c r="K17" s="11">
+        <f>I17/160</f>
+        <v/>
+      </c>
+      <c r="L17" s="3" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+      <c r="E18" s="9">
+        <f>'第1週'!L18</f>
+        <v/>
+      </c>
+      <c r="F18" s="9">
+        <f>'第2週'!L18</f>
+        <v/>
+      </c>
+      <c r="G18" s="9">
+        <f>'第3週'!L18</f>
+        <v/>
+      </c>
+      <c r="H18" s="9">
+        <f>'第4週'!L18</f>
+        <v/>
+      </c>
+      <c r="I18" s="10">
+        <f>SUM(E18:H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="10">
+        <f>I18/4</f>
+        <v/>
+      </c>
+      <c r="K18" s="11">
+        <f>I18/160</f>
+        <v/>
+      </c>
+      <c r="L18" s="3" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="9">
+        <f>'第1週'!L19</f>
+        <v/>
+      </c>
+      <c r="F19" s="9">
+        <f>'第2週'!L19</f>
+        <v/>
+      </c>
+      <c r="G19" s="9">
+        <f>'第3週'!L19</f>
+        <v/>
+      </c>
+      <c r="H19" s="9">
+        <f>'第4週'!L19</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>SUM(E19:H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>I19/4</f>
+        <v/>
+      </c>
+      <c r="K19" s="11">
+        <f>I19/160</f>
+        <v/>
+      </c>
+      <c r="L19" s="3" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="9">
+        <f>'第1週'!L20</f>
+        <v/>
+      </c>
+      <c r="F20" s="9">
+        <f>'第2週'!L20</f>
+        <v/>
+      </c>
+      <c r="G20" s="9">
+        <f>'第3週'!L20</f>
+        <v/>
+      </c>
+      <c r="H20" s="9">
+        <f>'第4週'!L20</f>
+        <v/>
+      </c>
+      <c r="I20" s="10">
+        <f>SUM(E20:H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="10">
+        <f>I20/4</f>
+        <v/>
+      </c>
+      <c r="K20" s="11">
+        <f>I20/160</f>
+        <v/>
+      </c>
+      <c r="L20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+      <c r="E21" s="9">
+        <f>'第1週'!L21</f>
+        <v/>
+      </c>
+      <c r="F21" s="9">
+        <f>'第2週'!L21</f>
+        <v/>
+      </c>
+      <c r="G21" s="9">
+        <f>'第3週'!L21</f>
+        <v/>
+      </c>
+      <c r="H21" s="9">
+        <f>'第4週'!L21</f>
+        <v/>
+      </c>
+      <c r="I21" s="10">
+        <f>SUM(E21:H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="10">
+        <f>I21/4</f>
+        <v/>
+      </c>
+      <c r="K21" s="11">
+        <f>I21/160</f>
+        <v/>
+      </c>
+      <c r="L21" s="3" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+      <c r="E22" s="9">
+        <f>'第1週'!L22</f>
+        <v/>
+      </c>
+      <c r="F22" s="9">
+        <f>'第2週'!L22</f>
+        <v/>
+      </c>
+      <c r="G22" s="9">
+        <f>'第3週'!L22</f>
+        <v/>
+      </c>
+      <c r="H22" s="9">
+        <f>'第4週'!L22</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>SUM(E22:H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10">
+        <f>I22/4</f>
+        <v/>
+      </c>
+      <c r="K22" s="11">
+        <f>I22/160</f>
+        <v/>
+      </c>
+      <c r="L22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="14">
+        <f>SUM(E8:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F8:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G8:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H8:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I8:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J8:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="15">
+        <f>SUM(K8:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>【人員配置基準】（地域密着型通所介護・利用定員18名）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>管理者</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>常勤専従1名（他の職務との兼務可）</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>生活相談員</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>サービス提供時間帯を通じて専従1名以上</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="5" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>看護職員</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>サービス提供時間帯を通じて専従1名以上</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>機能訓練指導員</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>1名以上（PT・OT・ST・看護職員・柔道整復師等）</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="5" t="n"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>介護職員</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>利用者15人まで1名以上、15人超は5名増ごとに+1名（定員18名→2名以上）</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>【入力の流れ】</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
+        <is>
+          <t>1. このシートの「職種」「雇用形態」「氏名」「備考」を入力します（各週シートには自動反映されます）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>2. シート下部の「第1週」〜「第4週」タブを開き、各曜日の勤務時間を入力します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>3. このシートの「4週合計」「月平均」「常勤換算（月/160h）」が自動計算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>※ 月の所定労働時間が160h（週40h×4週）と異なる場合は、K列の数式 =I/160 を変更してください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A26:L26"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="A33:L33"/>
+    <mergeCell ref="D28:L28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="D31:L31"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -649,7 +1701,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>勤務形態一覧表</t>
+          <t>勤務形態一覧表　第1週</t>
         </is>
       </c>
     </row>
@@ -664,6 +1716,10 @@
           <t>poem de riha 安積店</t>
         </is>
       </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>サービス種別</t>
@@ -674,6 +1730,12 @@
           <t>地域密着型通所介護（3時間以上4時間未満）／ 介護予防・日常生活支援総合事業</t>
         </is>
       </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -686,6 +1748,10 @@
           <t>福島県郡山市安積町笹川字四角担3-1</t>
         </is>
       </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>基準年月</t>
@@ -696,6 +1762,12 @@
           <t>令和8年（2026年）6月</t>
         </is>
       </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -708,6 +1780,10 @@
           <t>午前 9:00〜12:05 ／ 午後 13:25〜16:30</t>
         </is>
       </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>営業日</t>
@@ -718,755 +1794,3169 @@
           <t>月〜金（祝日も営業）／ 休：土日・年末年始</t>
         </is>
       </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>職種</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>雇用形態</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>火</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>金</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>土</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="K7" s="6" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>週合計
-(時間)</t>
-        </is>
-      </c>
-      <c r="M7" s="4" t="inlineStr">
+(h)</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>常勤換算
 (/40h)</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="N7" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="7">
+      <c r="B8" s="3">
+        <f>IF(集計!B8="","",集計!B8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(集計!C8="","",集計!C8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF(集計!D8="","",集計!D8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="10">
         <f>SUM(E8:K8)</f>
         <v/>
       </c>
-      <c r="M8" s="8">
+      <c r="M8" s="11">
         <f>L8/40</f>
         <v/>
       </c>
-      <c r="N8" s="9" t="inlineStr"/>
+      <c r="N8" s="3">
+        <f>IF(集計!L8="","",集計!L8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>生活相談員</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="7">
+      <c r="B9" s="3">
+        <f>IF(集計!B9="","",集計!B9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF(集計!C9="","",集計!C9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF(集計!D9="","",集計!D9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="10">
         <f>SUM(E9:K9)</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="11">
         <f>L9/40</f>
         <v/>
       </c>
-      <c r="N9" s="9" t="inlineStr"/>
+      <c r="N9" s="3">
+        <f>IF(集計!L9="","",集計!L9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>看護職員</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="7">
+      <c r="B10" s="3">
+        <f>IF(集計!B10="","",集計!B10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF(集計!C10="","",集計!C10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF(集計!D10="","",集計!D10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="10">
         <f>SUM(E10:K10)</f>
         <v/>
       </c>
-      <c r="M10" s="8">
+      <c r="M10" s="11">
         <f>L10/40</f>
         <v/>
       </c>
-      <c r="N10" s="9" t="inlineStr"/>
+      <c r="N10" s="3">
+        <f>IF(集計!L10="","",集計!L10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>機能訓練指導員</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="7">
+      <c r="B11" s="3">
+        <f>IF(集計!B11="","",集計!B11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF(集計!C11="","",集計!C11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF(集計!D11="","",集計!D11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="10">
         <f>SUM(E11:K11)</f>
         <v/>
       </c>
-      <c r="M11" s="8">
+      <c r="M11" s="11">
         <f>L11/40</f>
         <v/>
       </c>
-      <c r="N11" s="9" t="inlineStr">
-        <is>
-          <t>柔道整復師</t>
-        </is>
+      <c r="N11" s="3">
+        <f>IF(集計!L11="","",集計!L11)</f>
+        <v/>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>介護職員</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="7">
+      <c r="B12" s="3">
+        <f>IF(集計!B12="","",集計!B12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF(集計!C12="","",集計!C12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF(集計!D12="","",集計!D12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="10">
         <f>SUM(E12:K12)</f>
         <v/>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="11">
         <f>L12/40</f>
         <v/>
       </c>
-      <c r="N12" s="9" t="inlineStr"/>
+      <c r="N12" s="3">
+        <f>IF(集計!L12="","",集計!L12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>介護職員</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="7">
+      <c r="B13" s="3">
+        <f>IF(集計!B13="","",集計!B13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF(集計!C13="","",集計!C13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF(集計!D13="","",集計!D13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="10">
         <f>SUM(E13:K13)</f>
         <v/>
       </c>
-      <c r="M13" s="8">
+      <c r="M13" s="11">
         <f>L13/40</f>
         <v/>
       </c>
-      <c r="N13" s="9" t="inlineStr"/>
+      <c r="N13" s="3">
+        <f>IF(集計!L13="","",集計!L13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>介護職員</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>非常勤専従</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="7">
+      <c r="B14" s="3">
+        <f>IF(集計!B14="","",集計!B14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>IF(集計!C14="","",集計!C14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF(集計!D14="","",集計!D14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="10">
         <f>SUM(E14:K14)</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="11">
         <f>L14/40</f>
         <v/>
       </c>
-      <c r="N14" s="9" t="inlineStr"/>
+      <c r="N14" s="3">
+        <f>IF(集計!L14="","",集計!L14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>介護職員</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>非常勤専従</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="7">
+      <c r="B15" s="3">
+        <f>IF(集計!B15="","",集計!B15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>IF(集計!C15="","",集計!C15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF(集計!D15="","",集計!D15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="10">
         <f>SUM(E15:K15)</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="11">
         <f>L15/40</f>
         <v/>
       </c>
-      <c r="N15" s="9" t="inlineStr"/>
+      <c r="N15" s="3">
+        <f>IF(集計!L15="","",集計!L15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="7">
+      <c r="B16" s="3">
+        <f>IF(集計!B16="","",集計!B16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>IF(集計!C16="","",集計!C16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF(集計!D16="","",集計!D16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="10">
         <f>SUM(E16:K16)</f>
         <v/>
       </c>
-      <c r="M16" s="8">
+      <c r="M16" s="11">
         <f>L16/40</f>
         <v/>
       </c>
-      <c r="N16" s="9" t="n"/>
+      <c r="N16" s="3">
+        <f>IF(集計!L16="","",集計!L16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="7">
+      <c r="B17" s="3">
+        <f>IF(集計!B17="","",集計!B17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>IF(集計!C17="","",集計!C17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF(集計!D17="","",集計!D17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="10">
         <f>SUM(E17:K17)</f>
         <v/>
       </c>
-      <c r="M17" s="8">
+      <c r="M17" s="11">
         <f>L17/40</f>
         <v/>
       </c>
-      <c r="N17" s="9" t="n"/>
+      <c r="N17" s="3">
+        <f>IF(集計!L17="","",集計!L17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="7">
+      <c r="B18" s="3">
+        <f>IF(集計!B18="","",集計!B18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>IF(集計!C18="","",集計!C18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF(集計!D18="","",集計!D18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="10">
         <f>SUM(E18:K18)</f>
         <v/>
       </c>
-      <c r="M18" s="8">
+      <c r="M18" s="11">
         <f>L18/40</f>
         <v/>
       </c>
-      <c r="N18" s="9" t="n"/>
+      <c r="N18" s="3">
+        <f>IF(集計!L18="","",集計!L18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="7">
+      <c r="B19" s="3">
+        <f>IF(集計!B19="","",集計!B19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>IF(集計!C19="","",集計!C19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF(集計!D19="","",集計!D19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="10">
         <f>SUM(E19:K19)</f>
         <v/>
       </c>
-      <c r="M19" s="8">
+      <c r="M19" s="11">
         <f>L19/40</f>
         <v/>
       </c>
-      <c r="N19" s="9" t="n"/>
+      <c r="N19" s="3">
+        <f>IF(集計!L19="","",集計!L19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="7">
+      <c r="B20" s="3">
+        <f>IF(集計!B20="","",集計!B20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>IF(集計!C20="","",集計!C20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF(集計!D20="","",集計!D20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="10">
         <f>SUM(E20:K20)</f>
         <v/>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="11">
         <f>L20/40</f>
         <v/>
       </c>
-      <c r="N20" s="9" t="n"/>
+      <c r="N20" s="3">
+        <f>IF(集計!L20="","",集計!L20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="7">
+      <c r="B21" s="3">
+        <f>IF(集計!B21="","",集計!B21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>IF(集計!C21="","",集計!C21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF(集計!D21="","",集計!D21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="10">
         <f>SUM(E21:K21)</f>
         <v/>
       </c>
-      <c r="M21" s="8">
+      <c r="M21" s="11">
         <f>L21/40</f>
         <v/>
       </c>
-      <c r="N21" s="9" t="n"/>
+      <c r="N21" s="3">
+        <f>IF(集計!L21="","",集計!L21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="7">
+      <c r="B22" s="3">
+        <f>IF(集計!B22="","",集計!B22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>IF(集計!C22="","",集計!C22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF(集計!D22="","",集計!D22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="10">
         <f>SUM(E22:K22)</f>
         <v/>
       </c>
-      <c r="M22" s="8">
+      <c r="M22" s="11">
         <f>L22/40</f>
         <v/>
       </c>
-      <c r="N22" s="9" t="n"/>
+      <c r="N22" s="3">
+        <f>IF(集計!L22="","",集計!L22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12">
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="14">
         <f>SUM(E8:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="14">
         <f>SUM(F8:F22)</f>
         <v/>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="14">
         <f>SUM(G8:G22)</f>
         <v/>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="14">
         <f>SUM(H8:H22)</f>
         <v/>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="14">
         <f>SUM(I8:I22)</f>
         <v/>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="14">
         <f>SUM(J8:J22)</f>
         <v/>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="14">
         <f>SUM(K8:K22)</f>
         <v/>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="14">
         <f>SUM(L8:L22)</f>
         <v/>
       </c>
-      <c r="M23" s="13">
+      <c r="M23" s="15">
         <f>SUM(M8:M22)</f>
         <v/>
       </c>
-      <c r="N23" s="11" t="n"/>
+      <c r="N23" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>※ 各曜日の勤務時間を「時間」単位（例：8、7.5、4）で入力してください。</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>【人員配置基準】（地域密着型通所介護・利用定員18名）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>管理者</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>常勤専従1名（他の職務との兼務可）</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="15" t="n"/>
-      <c r="J27" s="15" t="n"/>
-      <c r="K27" s="15" t="n"/>
-      <c r="L27" s="15" t="n"/>
-      <c r="M27" s="15" t="n"/>
-      <c r="N27" s="16" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>生活相談員</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>サービス提供時間帯を通じて専従1名以上</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="15" t="n"/>
-      <c r="J28" s="15" t="n"/>
-      <c r="K28" s="15" t="n"/>
-      <c r="L28" s="15" t="n"/>
-      <c r="M28" s="15" t="n"/>
-      <c r="N28" s="16" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>看護職員</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>サービス提供時間帯を通じて専従1名以上</t>
-        </is>
-      </c>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="15" t="n"/>
-      <c r="J29" s="15" t="n"/>
-      <c r="K29" s="15" t="n"/>
-      <c r="L29" s="15" t="n"/>
-      <c r="M29" s="15" t="n"/>
-      <c r="N29" s="16" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>機能訓練指導員</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>1名以上（PT・OT・ST・看護職員・柔道整復師等）</t>
-        </is>
-      </c>
-      <c r="E30" s="15" t="n"/>
-      <c r="F30" s="15" t="n"/>
-      <c r="G30" s="15" t="n"/>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="15" t="n"/>
-      <c r="J30" s="15" t="n"/>
-      <c r="K30" s="15" t="n"/>
-      <c r="L30" s="15" t="n"/>
-      <c r="M30" s="15" t="n"/>
-      <c r="N30" s="16" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>介護職員</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>利用者15人まで1名以上、15人を超えて5又はその端数増ごとに+1名（定員18名→2名以上）</t>
-        </is>
-      </c>
-      <c r="E31" s="15" t="n"/>
-      <c r="F31" s="15" t="n"/>
-      <c r="G31" s="15" t="n"/>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="15" t="n"/>
-      <c r="J31" s="15" t="n"/>
-      <c r="K31" s="15" t="n"/>
-      <c r="L31" s="15" t="n"/>
-      <c r="M31" s="15" t="n"/>
-      <c r="N31" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>【入力の注意】</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>・各曜日の勤務時間を「時間」単位（小数可、例：8、7.5、4）で入力してください。週合計と常勤換算は自動計算されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>・常勤換算の分母は「週40時間」です。事業所の常勤所定労働時間が異なる場合は M列の数式（=L/40）を変更してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
-        <is>
-          <t>・雇用形態は「常勤専従」「常勤兼務」「非常勤専従」「非常勤兼務」のいずれかを記入。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>・1名で複数職種を兼ねる場合は、職種ごとに行を分け、勤務時間を分割して記入してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
-        <is>
-          <t>・行が足りない場合は最終行を選択してコピー＆挿入してください（数式も追従します）。</t>
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>※ 職種・雇用形態・氏名は「集計」シートから自動表示されます（直接編集も可能）。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="10">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H5:N5"/>
     <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A34:N34"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="A26:N26"/>
     <mergeCell ref="H3:N3"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A36:N36"/>
-    <mergeCell ref="D31:N31"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A25:N25"/>
     <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務形態一覧表　第2週</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>poem de riha 安積店</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護（3時間以上4時間未満）／ 介護予防・日常生活支援総合事業</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>福島県郡山市安積町笹川字四角担3-1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>基準年月</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>令和8年（2026年）6月</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>サービス提供時間</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>午前 9:00〜12:05 ／ 午後 13:25〜16:30</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>営業日</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>月〜金（祝日も営業）／ 休：土日・年末年始</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>雇用形態</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>週合計
+(h)</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>常勤換算
+(/40h)</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <f>IF(集計!B8="","",集計!B8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(集計!C8="","",集計!C8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF(集計!D8="","",集計!D8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="10">
+        <f>SUM(E8:K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="11">
+        <f>L8/40</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF(集計!L8="","",集計!L8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3">
+        <f>IF(集計!B9="","",集計!B9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF(集計!C9="","",集計!C9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF(集計!D9="","",集計!D9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="10">
+        <f>SUM(E9:K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="11">
+        <f>L9/40</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF(集計!L9="","",集計!L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <f>IF(集計!B10="","",集計!B10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF(集計!C10="","",集計!C10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF(集計!D10="","",集計!D10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="10">
+        <f>SUM(E10:K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>L10/40</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF(集計!L10="","",集計!L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3">
+        <f>IF(集計!B11="","",集計!B11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF(集計!C11="","",集計!C11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF(集計!D11="","",集計!D11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="10">
+        <f>SUM(E11:K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>L11/40</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF(集計!L11="","",集計!L11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <f>IF(集計!B12="","",集計!B12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF(集計!C12="","",集計!C12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF(集計!D12="","",集計!D12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="10">
+        <f>SUM(E12:K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>L12/40</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF(集計!L12="","",集計!L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3">
+        <f>IF(集計!B13="","",集計!B13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF(集計!C13="","",集計!C13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF(集計!D13="","",集計!D13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="10">
+        <f>SUM(E13:K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>L13/40</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF(集計!L13="","",集計!L13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3">
+        <f>IF(集計!B14="","",集計!B14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>IF(集計!C14="","",集計!C14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF(集計!D14="","",集計!D14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="10">
+        <f>SUM(E14:K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="11">
+        <f>L14/40</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>IF(集計!L14="","",集計!L14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(集計!B15="","",集計!B15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>IF(集計!C15="","",集計!C15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF(集計!D15="","",集計!D15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="10">
+        <f>SUM(E15:K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11">
+        <f>L15/40</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>IF(集計!L15="","",集計!L15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3">
+        <f>IF(集計!B16="","",集計!B16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>IF(集計!C16="","",集計!C16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF(集計!D16="","",集計!D16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="10">
+        <f>SUM(E16:K16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f>L16/40</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(集計!L16="","",集計!L16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3">
+        <f>IF(集計!B17="","",集計!B17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>IF(集計!C17="","",集計!C17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF(集計!D17="","",集計!D17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="10">
+        <f>SUM(E17:K17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>L17/40</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(集計!L17="","",集計!L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3">
+        <f>IF(集計!B18="","",集計!B18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>IF(集計!C18="","",集計!C18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF(集計!D18="","",集計!D18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="10">
+        <f>SUM(E18:K18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>L18/40</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>IF(集計!L18="","",集計!L18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3">
+        <f>IF(集計!B19="","",集計!B19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>IF(集計!C19="","",集計!C19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF(集計!D19="","",集計!D19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="10">
+        <f>SUM(E19:K19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="11">
+        <f>L19/40</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>IF(集計!L19="","",集計!L19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <f>IF(集計!B20="","",集計!B20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>IF(集計!C20="","",集計!C20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF(集計!D20="","",集計!D20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="10">
+        <f>SUM(E20:K20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11">
+        <f>L20/40</f>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f>IF(集計!L20="","",集計!L20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
+        <f>IF(集計!B21="","",集計!B21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>IF(集計!C21="","",集計!C21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF(集計!D21="","",集計!D21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="10">
+        <f>SUM(E21:K21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="11">
+        <f>L21/40</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>IF(集計!L21="","",集計!L21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
+        <f>IF(集計!B22="","",集計!B22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>IF(集計!C22="","",集計!C22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF(集計!D22="","",集計!D22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="10">
+        <f>SUM(E22:K22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11">
+        <f>L22/40</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IF(集計!L22="","",集計!L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="14">
+        <f>SUM(E8:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F8:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G8:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H8:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I8:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J8:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K8:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L8:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="15">
+        <f>SUM(M8:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>※ 各曜日の勤務時間を「時間」単位（例：8、7.5、4）で入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>※ 職種・雇用形態・氏名は「集計」シートから自動表示されます（直接編集も可能）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B4:F4"/>
     <mergeCell ref="H5:N5"/>
-    <mergeCell ref="D27:N27"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A37:N37"/>
-    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A23:D23"/>
     <mergeCell ref="H4:N4"/>
     <mergeCell ref="A26:N26"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A33:N33"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D28:N28"/>
-    <mergeCell ref="A35:N35"/>
-    <mergeCell ref="D30:N30"/>
-    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="D29:N29"/>
+    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務形態一覧表　第3週</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>poem de riha 安積店</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護（3時間以上4時間未満）／ 介護予防・日常生活支援総合事業</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>福島県郡山市安積町笹川字四角担3-1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>基準年月</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>令和8年（2026年）6月</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>サービス提供時間</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>午前 9:00〜12:05 ／ 午後 13:25〜16:30</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>営業日</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>月〜金（祝日も営業）／ 休：土日・年末年始</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>雇用形態</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>週合計
+(h)</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>常勤換算
+(/40h)</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <f>IF(集計!B8="","",集計!B8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(集計!C8="","",集計!C8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF(集計!D8="","",集計!D8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="10">
+        <f>SUM(E8:K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="11">
+        <f>L8/40</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF(集計!L8="","",集計!L8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3">
+        <f>IF(集計!B9="","",集計!B9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF(集計!C9="","",集計!C9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF(集計!D9="","",集計!D9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="10">
+        <f>SUM(E9:K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="11">
+        <f>L9/40</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF(集計!L9="","",集計!L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <f>IF(集計!B10="","",集計!B10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF(集計!C10="","",集計!C10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF(集計!D10="","",集計!D10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="10">
+        <f>SUM(E10:K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>L10/40</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF(集計!L10="","",集計!L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3">
+        <f>IF(集計!B11="","",集計!B11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF(集計!C11="","",集計!C11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF(集計!D11="","",集計!D11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="10">
+        <f>SUM(E11:K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>L11/40</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF(集計!L11="","",集計!L11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <f>IF(集計!B12="","",集計!B12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF(集計!C12="","",集計!C12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF(集計!D12="","",集計!D12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="10">
+        <f>SUM(E12:K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>L12/40</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF(集計!L12="","",集計!L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3">
+        <f>IF(集計!B13="","",集計!B13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF(集計!C13="","",集計!C13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF(集計!D13="","",集計!D13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="10">
+        <f>SUM(E13:K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>L13/40</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF(集計!L13="","",集計!L13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3">
+        <f>IF(集計!B14="","",集計!B14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>IF(集計!C14="","",集計!C14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF(集計!D14="","",集計!D14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="10">
+        <f>SUM(E14:K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="11">
+        <f>L14/40</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>IF(集計!L14="","",集計!L14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(集計!B15="","",集計!B15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>IF(集計!C15="","",集計!C15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF(集計!D15="","",集計!D15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="10">
+        <f>SUM(E15:K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11">
+        <f>L15/40</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>IF(集計!L15="","",集計!L15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3">
+        <f>IF(集計!B16="","",集計!B16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>IF(集計!C16="","",集計!C16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF(集計!D16="","",集計!D16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="10">
+        <f>SUM(E16:K16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f>L16/40</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(集計!L16="","",集計!L16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3">
+        <f>IF(集計!B17="","",集計!B17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>IF(集計!C17="","",集計!C17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF(集計!D17="","",集計!D17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="10">
+        <f>SUM(E17:K17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>L17/40</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(集計!L17="","",集計!L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3">
+        <f>IF(集計!B18="","",集計!B18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>IF(集計!C18="","",集計!C18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF(集計!D18="","",集計!D18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="10">
+        <f>SUM(E18:K18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>L18/40</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>IF(集計!L18="","",集計!L18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3">
+        <f>IF(集計!B19="","",集計!B19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>IF(集計!C19="","",集計!C19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF(集計!D19="","",集計!D19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="10">
+        <f>SUM(E19:K19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="11">
+        <f>L19/40</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>IF(集計!L19="","",集計!L19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <f>IF(集計!B20="","",集計!B20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>IF(集計!C20="","",集計!C20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF(集計!D20="","",集計!D20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="10">
+        <f>SUM(E20:K20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11">
+        <f>L20/40</f>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f>IF(集計!L20="","",集計!L20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
+        <f>IF(集計!B21="","",集計!B21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>IF(集計!C21="","",集計!C21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF(集計!D21="","",集計!D21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="10">
+        <f>SUM(E21:K21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="11">
+        <f>L21/40</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>IF(集計!L21="","",集計!L21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
+        <f>IF(集計!B22="","",集計!B22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>IF(集計!C22="","",集計!C22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF(集計!D22="","",集計!D22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="10">
+        <f>SUM(E22:K22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11">
+        <f>L22/40</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IF(集計!L22="","",集計!L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="14">
+        <f>SUM(E8:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F8:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G8:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H8:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I8:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J8:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K8:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L8:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="15">
+        <f>SUM(M8:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>※ 各曜日の勤務時間を「時間」単位（例：8、7.5、4）で入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>※ 職種・雇用形態・氏名は「集計」シートから自動表示されます（直接編集も可能）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>勤務形態一覧表　第4週</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>事業所名</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>poem de riha 安積店</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>地域密着型通所介護（3時間以上4時間未満）／ 介護予防・日常生活支援総合事業</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+      <c r="L3" s="4" t="n"/>
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>所在地</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>福島県郡山市安積町笹川字四角担3-1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>基準年月</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>令和8年（2026年）6月</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
+      <c r="L4" s="4" t="n"/>
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>サービス提供時間</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>午前 9:00〜12:05 ／ 午後 13:25〜16:30</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>営業日</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>月〜金（祝日も営業）／ 休：土日・年末年始</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="5" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>職種</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>雇用形態</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>週合計
+(h)</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>常勤換算
+(/40h)</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="3">
+        <f>IF(集計!B8="","",集計!B8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>IF(集計!C8="","",集計!C8)</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>IF(集計!D8="","",集計!D8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="19" t="n"/>
+      <c r="G8" s="19" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="19" t="n"/>
+      <c r="L8" s="10">
+        <f>SUM(E8:K8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="11">
+        <f>L8/40</f>
+        <v/>
+      </c>
+      <c r="N8" s="3">
+        <f>IF(集計!L8="","",集計!L8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3">
+        <f>IF(集計!B9="","",集計!B9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>IF(集計!C9="","",集計!C9)</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>IF(集計!D9="","",集計!D9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="19" t="n"/>
+      <c r="G9" s="19" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="19" t="n"/>
+      <c r="L9" s="10">
+        <f>SUM(E9:K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="11">
+        <f>L9/40</f>
+        <v/>
+      </c>
+      <c r="N9" s="3">
+        <f>IF(集計!L9="","",集計!L9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="3">
+        <f>IF(集計!B10="","",集計!B10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="3">
+        <f>IF(集計!C10="","",集計!C10)</f>
+        <v/>
+      </c>
+      <c r="D10" s="3">
+        <f>IF(集計!D10="","",集計!D10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="19" t="n"/>
+      <c r="G10" s="19" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="19" t="n"/>
+      <c r="L10" s="10">
+        <f>SUM(E10:K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="11">
+        <f>L10/40</f>
+        <v/>
+      </c>
+      <c r="N10" s="3">
+        <f>IF(集計!L10="","",集計!L10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3">
+        <f>IF(集計!B11="","",集計!B11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>IF(集計!C11="","",集計!C11)</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>IF(集計!D11="","",集計!D11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="19" t="n"/>
+      <c r="G11" s="19" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="19" t="n"/>
+      <c r="L11" s="10">
+        <f>SUM(E11:K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="11">
+        <f>L11/40</f>
+        <v/>
+      </c>
+      <c r="N11" s="3">
+        <f>IF(集計!L11="","",集計!L11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3">
+        <f>IF(集計!B12="","",集計!B12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="3">
+        <f>IF(集計!C12="","",集計!C12)</f>
+        <v/>
+      </c>
+      <c r="D12" s="3">
+        <f>IF(集計!D12="","",集計!D12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="19" t="n"/>
+      <c r="G12" s="19" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="19" t="n"/>
+      <c r="L12" s="10">
+        <f>SUM(E12:K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="11">
+        <f>L12/40</f>
+        <v/>
+      </c>
+      <c r="N12" s="3">
+        <f>IF(集計!L12="","",集計!L12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="3">
+        <f>IF(集計!B13="","",集計!B13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>IF(集計!C13="","",集計!C13)</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>IF(集計!D13="","",集計!D13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="19" t="n"/>
+      <c r="G13" s="19" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="19" t="n"/>
+      <c r="L13" s="10">
+        <f>SUM(E13:K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="11">
+        <f>L13/40</f>
+        <v/>
+      </c>
+      <c r="N13" s="3">
+        <f>IF(集計!L13="","",集計!L13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="3">
+        <f>IF(集計!B14="","",集計!B14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="3">
+        <f>IF(集計!C14="","",集計!C14)</f>
+        <v/>
+      </c>
+      <c r="D14" s="3">
+        <f>IF(集計!D14="","",集計!D14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="10">
+        <f>SUM(E14:K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="11">
+        <f>L14/40</f>
+        <v/>
+      </c>
+      <c r="N14" s="3">
+        <f>IF(集計!L14="","",集計!L14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3">
+        <f>IF(集計!B15="","",集計!B15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="3">
+        <f>IF(集計!C15="","",集計!C15)</f>
+        <v/>
+      </c>
+      <c r="D15" s="3">
+        <f>IF(集計!D15="","",集計!D15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="10">
+        <f>SUM(E15:K15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="11">
+        <f>L15/40</f>
+        <v/>
+      </c>
+      <c r="N15" s="3">
+        <f>IF(集計!L15="","",集計!L15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3">
+        <f>IF(集計!B16="","",集計!B16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>IF(集計!C16="","",集計!C16)</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>IF(集計!D16="","",集計!D16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="19" t="n"/>
+      <c r="L16" s="10">
+        <f>SUM(E16:K16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="11">
+        <f>L16/40</f>
+        <v/>
+      </c>
+      <c r="N16" s="3">
+        <f>IF(集計!L16="","",集計!L16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3">
+        <f>IF(集計!B17="","",集計!B17)</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>IF(集計!C17="","",集計!C17)</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>IF(集計!D17="","",集計!D17)</f>
+        <v/>
+      </c>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="19" t="n"/>
+      <c r="L17" s="10">
+        <f>SUM(E17:K17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="11">
+        <f>L17/40</f>
+        <v/>
+      </c>
+      <c r="N17" s="3">
+        <f>IF(集計!L17="","",集計!L17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3">
+        <f>IF(集計!B18="","",集計!B18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>IF(集計!C18="","",集計!C18)</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>IF(集計!D18="","",集計!D18)</f>
+        <v/>
+      </c>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="19" t="n"/>
+      <c r="L18" s="10">
+        <f>SUM(E18:K18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="11">
+        <f>L18/40</f>
+        <v/>
+      </c>
+      <c r="N18" s="3">
+        <f>IF(集計!L18="","",集計!L18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3">
+        <f>IF(集計!B19="","",集計!B19)</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>IF(集計!C19="","",集計!C19)</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>IF(集計!D19="","",集計!D19)</f>
+        <v/>
+      </c>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="19" t="n"/>
+      <c r="G19" s="19" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="19" t="n"/>
+      <c r="L19" s="10">
+        <f>SUM(E19:K19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="11">
+        <f>L19/40</f>
+        <v/>
+      </c>
+      <c r="N19" s="3">
+        <f>IF(集計!L19="","",集計!L19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3">
+        <f>IF(集計!B20="","",集計!B20)</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>IF(集計!C20="","",集計!C20)</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>IF(集計!D20="","",集計!D20)</f>
+        <v/>
+      </c>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="19" t="n"/>
+      <c r="G20" s="19" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="10">
+        <f>SUM(E20:K20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="11">
+        <f>L20/40</f>
+        <v/>
+      </c>
+      <c r="N20" s="3">
+        <f>IF(集計!L20="","",集計!L20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3">
+        <f>IF(集計!B21="","",集計!B21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>IF(集計!C21="","",集計!C21)</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>IF(集計!D21="","",集計!D21)</f>
+        <v/>
+      </c>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="19" t="n"/>
+      <c r="G21" s="19" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="19" t="n"/>
+      <c r="L21" s="10">
+        <f>SUM(E21:K21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="11">
+        <f>L21/40</f>
+        <v/>
+      </c>
+      <c r="N21" s="3">
+        <f>IF(集計!L21="","",集計!L21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3">
+        <f>IF(集計!B22="","",集計!B22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>IF(集計!C22="","",集計!C22)</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>IF(集計!D22="","",集計!D22)</f>
+        <v/>
+      </c>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="19" t="n"/>
+      <c r="G22" s="19" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="19" t="n"/>
+      <c r="L22" s="10">
+        <f>SUM(E22:K22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="11">
+        <f>L22/40</f>
+        <v/>
+      </c>
+      <c r="N22" s="3">
+        <f>IF(集計!L22="","",集計!L22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="14">
+        <f>SUM(E8:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>SUM(F8:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>SUM(G8:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="14">
+        <f>SUM(H8:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="14">
+        <f>SUM(I8:I22)</f>
+        <v/>
+      </c>
+      <c r="J23" s="14">
+        <f>SUM(J8:J22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="14">
+        <f>SUM(K8:K22)</f>
+        <v/>
+      </c>
+      <c r="L23" s="14">
+        <f>SUM(L8:L22)</f>
+        <v/>
+      </c>
+      <c r="M23" s="15">
+        <f>SUM(M8:M22)</f>
+        <v/>
+      </c>
+      <c r="N23" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>※ 各曜日の勤務時間を「時間」単位（例：8、7.5、4）で入力してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>※ 職種・雇用形態・氏名は「集計」シートから自動表示されます（直接編集も可能）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="A26:N26"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/docs/poem-asaka-shift-schedule.xlsx
+++ b/docs/poem-asaka-shift-schedule.xlsx
@@ -10,9 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シフトパターン" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="勤務形態一覧表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="シフトコード">'シフトパターン'!$A$5:$A$23</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1667,7 +1665,7 @@
       <c r="AE9" s="14" t="n"/>
       <c r="AF9" s="14" t="n"/>
       <c r="AG9" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E9:AF9,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E9:AF9,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH9" s="6">
@@ -1724,7 +1722,7 @@
       <c r="AE10" s="14" t="n"/>
       <c r="AF10" s="14" t="n"/>
       <c r="AG10" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E10:AF10,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E10:AF10,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH10" s="6">
@@ -1781,7 +1779,7 @@
       <c r="AE11" s="14" t="n"/>
       <c r="AF11" s="14" t="n"/>
       <c r="AG11" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E11:AF11,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E11:AF11,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH11" s="6">
@@ -1838,7 +1836,7 @@
       <c r="AE12" s="14" t="n"/>
       <c r="AF12" s="14" t="n"/>
       <c r="AG12" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E12:AF12,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E12:AF12,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH12" s="6">
@@ -1899,7 +1897,7 @@
       <c r="AE13" s="14" t="n"/>
       <c r="AF13" s="14" t="n"/>
       <c r="AG13" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E13:AF13,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E13:AF13,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH13" s="6">
@@ -1956,7 +1954,7 @@
       <c r="AE14" s="14" t="n"/>
       <c r="AF14" s="14" t="n"/>
       <c r="AG14" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E14:AF14,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E14:AF14,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH14" s="6">
@@ -2013,7 +2011,7 @@
       <c r="AE15" s="14" t="n"/>
       <c r="AF15" s="14" t="n"/>
       <c r="AG15" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E15:AF15,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E15:AF15,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH15" s="6">
@@ -2070,7 +2068,7 @@
       <c r="AE16" s="14" t="n"/>
       <c r="AF16" s="14" t="n"/>
       <c r="AG16" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E16:AF16,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E16:AF16,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH16" s="6">
@@ -2119,7 +2117,7 @@
       <c r="AE17" s="14" t="n"/>
       <c r="AF17" s="14" t="n"/>
       <c r="AG17" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E17:AF17,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E17:AF17,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH17" s="6">
@@ -2168,7 +2166,7 @@
       <c r="AE18" s="14" t="n"/>
       <c r="AF18" s="14" t="n"/>
       <c r="AG18" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E18:AF18,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E18:AF18,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH18" s="6">
@@ -2217,7 +2215,7 @@
       <c r="AE19" s="14" t="n"/>
       <c r="AF19" s="14" t="n"/>
       <c r="AG19" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E19:AF19,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E19:AF19,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH19" s="6">
@@ -2266,7 +2264,7 @@
       <c r="AE20" s="14" t="n"/>
       <c r="AF20" s="14" t="n"/>
       <c r="AG20" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E20:AF20,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E20:AF20,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH20" s="6">
@@ -2315,7 +2313,7 @@
       <c r="AE21" s="14" t="n"/>
       <c r="AF21" s="14" t="n"/>
       <c r="AG21" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E21:AF21,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E21:AF21,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH21" s="6">
@@ -2364,7 +2362,7 @@
       <c r="AE22" s="14" t="n"/>
       <c r="AF22" s="14" t="n"/>
       <c r="AG22" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E22:AF22,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E22:AF22,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH22" s="6">
@@ -2413,7 +2411,7 @@
       <c r="AE23" s="14" t="n"/>
       <c r="AF23" s="14" t="n"/>
       <c r="AG23" s="6">
-        <f>SUMPRODUCT(IFERROR(VLOOKUP(E23:AF23,シフトパターン!$A$5:$F$23,6,FALSE),0))</f>
+        <f>SUMPRODUCT(COUNTIF(E23:AF23,シフトパターン!$A$5:$A$23),シフトパターン!$F$5:$F$23)</f>
         <v/>
       </c>
       <c r="AH23" s="6">
@@ -2804,7 +2802,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E9:AF9 E10:AF10 E11:AF11 E12:AF12 E13:AF13 E14:AF14 E15:AF15 E16:AF16 E17:AF17 E18:AF18 E19:AF19 E20:AF20 E21:AF21 E22:AF22 E23:AF23" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="無効なシフトコード" error="シフトパターンに登録されたコードを選択してください" promptTitle="シフト入力" prompt="シフトコードを選択" type="list">
-      <formula1>=シフトコード</formula1>
+      <formula1>=シフトパターン!$A$5:$A$23</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/docs/poem-asaka-shift-schedule.xlsx
+++ b/docs/poem-asaka-shift-schedule.xlsx
@@ -2802,7 +2802,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="E9:AF9 E10:AF10 E11:AF11 E12:AF12 E13:AF13 E14:AF14 E15:AF15 E16:AF16 E17:AF17 E18:AF18 E19:AF19 E20:AF20 E21:AF21 E22:AF22 E23:AF23" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="無効なシフトコード" error="シフトパターンに登録されたコードを選択してください" promptTitle="シフト入力" prompt="シフトコードを選択" type="list">
-      <formula1>=シフトパターン!$A$5:$A$23</formula1>
+      <formula1>"早,日,遅,A,B,通,半早,半遅,夜,短,有,特,公,休"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
